--- a/estimulos.xlsx
+++ b/estimulos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app 1.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712BBF99-E1F9-4600-AD17-78C6BBD8523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836EAEF5-2075-4B57-9C9A-4F95CE2BDA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6D91FCCA-5E0A-4D09-BD20-3C3DC9828942}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>id_estimulo</t>
   </si>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>Primero deberás analizar una imagen. Luego responder algunas preguntas.</t>
+  </si>
+  <si>
+    <t>Primero podrás estudiar la tabla del 6. Luego deberás responder algunas preguntas.</t>
+  </si>
+  <si>
+    <t>tabla6.jpg</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3D7AE0-F17D-4647-96C4-DA9C95D5956E}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -754,6 +760,20 @@
         <v>30</v>
       </c>
     </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
